--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,51 @@
         <v>69</v>
       </c>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>00:01:39</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-20.28</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>609.4 Hz | 914.1 Hz | 1257.8 Hz</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2502</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11839</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,6 +558,51 @@
         <v>11839</v>
       </c>
       <c r="K3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>00:03:02</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-23.07</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>656.2 Hz | 921.9 Hz | 1234.4 Hz</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2518</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28058</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,6 +605,51 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>00:03:34</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-22.39</v>
+      </c>
+      <c r="G5" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>937.5 Hz | 1421.9 Hz | 1851.6 Hz</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2514</v>
+      </c>
+      <c r="J5" t="n">
+        <v>73</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
         </is>
       </c>
     </row>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -650,6 +650,51 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>00:04:47</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-23.55</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>648.4 Hz | 921.9 Hz | 1234.4 Hz</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2535</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11662</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +695,51 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20:11:45</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-24.74</v>
+      </c>
+      <c r="G7" t="n">
+        <v>94.91</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>953.1 Hz | 1421.9 Hz | 1898.4 Hz</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2560</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10650</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
         </is>
       </c>
     </row>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,6 +740,51 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20:13:46</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>281.25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-18.26</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>562.5 Hz | 843.8 Hz | 1164.1 Hz</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2560</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12366</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,51 @@
         <v>12366</v>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20:14:30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>500</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-23.67</v>
+      </c>
+      <c r="G9" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1000.0 Hz | 1492.2 Hz | 2015.6 Hz</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2543</v>
+      </c>
+      <c r="J9" t="n">
+        <v>61</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,6 +833,51 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20:16:31</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>500</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-24.14</v>
+      </c>
+      <c r="G10" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1000.0 Hz | 1492.2 Hz | 2015.6 Hz</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2492</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10307</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,51 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20:16:56</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>500</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-25.32</v>
+      </c>
+      <c r="G11" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1000.0 Hz | 1492.2 Hz | 2015.6 Hz</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2555</v>
+      </c>
+      <c r="J11" t="n">
+        <v>57</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +923,51 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20:17:47</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>710.9 Hz | 1062.5 Hz | 1421.9 Hz</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2513</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10239</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -968,6 +968,51 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:18:32</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-24.49</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>593.8 Hz | 1007.8 Hz | 1234.4 Hz</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2541</v>
+      </c>
+      <c r="J13" t="n">
+        <v>57</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,51 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20:18:49</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-27.44</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>648.4 Hz | 1007.8 Hz | 1234.4 Hz</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2535</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10274</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,6 +1058,51 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20:19:12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-24.34</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>960.9 Hz | 1445.3 Hz | 1937.5 Hz</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2541</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10331</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,6 +1103,51 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:19:36</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-23.91</v>
+      </c>
+      <c r="G16" t="n">
+        <v>88.47</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>968.8 Hz | 1453.1 Hz | 1937.5 Hz</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2522</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10974</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>🚨 SÍ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,6 +1148,51 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20:20:34</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>593.8 Hz | 914.1 Hz | 1234.4 Hz</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2545</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10241</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1193,51 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:20:58</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>875</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-20.19</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1742.2 Hz | 2617.2 Hz | 3484.4 Hz</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2502</v>
+      </c>
+      <c r="J18" t="n">
+        <v>57</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,6 +1238,51 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>20:21:29</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>875</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-23.98</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1742.2 Hz | 2617.2 Hz | 3484.4 Hz</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2545</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10203</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1283,6 +1283,51 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20:21:44</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>335.94</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-19.94</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>710.9 Hz | 984.4 Hz | 1296.9 Hz</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2529</v>
+      </c>
+      <c r="J20" t="n">
+        <v>11188</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1328,6 +1328,51 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20:22:09</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1671.88</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-22.28</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3335.9 Hz | 4984.4 Hz | 6718.8 Hz</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2542</v>
+      </c>
+      <c r="J21" t="n">
+        <v>60</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datos/excel/reporte_2026-05-29.xlsx
+++ b/datos/excel/reporte_2026-05-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1373,6 +1373,51 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:22:22</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-21.67</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>632.8 Hz | 929.7 Hz | 1296.9 Hz</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2499</v>
+      </c>
+      <c r="J22" t="n">
+        <v>10638</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
